--- a/reference_outputs/cohort_tables/COMAVI_all_variants_master.xlsx
+++ b/reference_outputs/cohort_tables/COMAVI_all_variants_master.xlsx
@@ -3487,7 +3487,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ppi_destab_mechanism</t>
+          <t>structurally_silent</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ppi_destab_mechanism</t>
+          <t>structurally_silent</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ppi_destab_mechanism</t>
+          <t>structurally_silent</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>destab</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -21523,67 +21523,67 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="S30" t="b">
@@ -21616,67 +21616,67 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="S31" t="b">
@@ -22546,43 +22546,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
